--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125491343</v>
+        <v>125491323</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>58305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125492212</v>
+        <v>125491467</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,11 +832,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491326</v>
+        <v>125491594</v>
       </c>
       <c r="B4" t="n">
-        <v>57847</v>
+        <v>58060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125491323</v>
+        <v>125492610</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>57030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1055,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100091</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1134,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125492610</v>
+        <v>125491333</v>
       </c>
       <c r="B6" t="n">
-        <v>56942</v>
+        <v>57053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100091</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1258,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125491467</v>
+        <v>125492212</v>
       </c>
       <c r="B7" t="n">
-        <v>56725</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,20 +1303,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1328,7 +1324,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125491594</v>
+        <v>125491326</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>57961</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125491333</v>
+        <v>125491343</v>
       </c>
       <c r="B9" t="n">
-        <v>56965</v>
+        <v>58001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491594</v>
+        <v>125492610</v>
       </c>
       <c r="B4" t="n">
-        <v>58060</v>
+        <v>57030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>100091</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125492610</v>
+        <v>125491594</v>
       </c>
       <c r="B5" t="n">
-        <v>57030</v>
+        <v>58060</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100091</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125491323</v>
+        <v>125491594</v>
       </c>
       <c r="B2" t="n">
-        <v>58305</v>
+        <v>58060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125491594</v>
+        <v>125491333</v>
       </c>
       <c r="B5" t="n">
-        <v>58060</v>
+        <v>57053</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125491333</v>
+        <v>125492212</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125492212</v>
+        <v>125491326</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57961</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125491326</v>
+        <v>125491343</v>
       </c>
       <c r="B8" t="n">
-        <v>57961</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,20 +1427,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125491343</v>
+        <v>125491323</v>
       </c>
       <c r="B9" t="n">
-        <v>58001</v>
+        <v>58305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125491467</v>
+        <v>125491333</v>
       </c>
       <c r="B3" t="n">
-        <v>56846</v>
+        <v>57063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491333</v>
+        <v>125491467</v>
       </c>
       <c r="B4" t="n">
-        <v>57063</v>
+        <v>56846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,11 +941,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125491326</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125491333</v>
+        <v>125491467</v>
       </c>
       <c r="B3" t="n">
-        <v>57063</v>
+        <v>56846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,11 +822,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491467</v>
+        <v>125491333</v>
       </c>
       <c r="B4" t="n">
-        <v>56846</v>
+        <v>57063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,7 +937,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1269,7 +1269,7 @@
         <v>125491594</v>
       </c>
       <c r="B7" t="n">
-        <v>58078</v>
+        <v>58079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>125491343</v>
       </c>
       <c r="B8" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>125491323</v>
       </c>
       <c r="B9" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125491333</v>
+        <v>125491467</v>
       </c>
       <c r="B3" t="n">
-        <v>57063</v>
+        <v>56846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,11 +822,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491467</v>
+        <v>125491333</v>
       </c>
       <c r="B4" t="n">
-        <v>56846</v>
+        <v>57063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,7 +937,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125491326</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125491333</v>
       </c>
       <c r="B3" t="n">
-        <v>57063</v>
+        <v>57064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>125491467</v>
       </c>
       <c r="B4" t="n">
-        <v>56846</v>
+        <v>56847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>125492212</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>125492610</v>
       </c>
       <c r="B6" t="n">
-        <v>57040</v>
+        <v>57041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125491594</v>
       </c>
       <c r="B7" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>125491343</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>125491323</v>
       </c>
       <c r="B9" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125491333</v>
+        <v>125491467</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>56847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,11 +822,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491467</v>
+        <v>125491333</v>
       </c>
       <c r="B4" t="n">
-        <v>56847</v>
+        <v>57064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,7 +937,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125491326</v>
+        <v>109329758</v>
       </c>
       <c r="B2" t="n">
-        <v>57981</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -712,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R2" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125491467</v>
+        <v>109330094</v>
       </c>
       <c r="B3" t="n">
-        <v>56847</v>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R3" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125491333</v>
+        <v>109329712</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R4" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125492212</v>
+        <v>109330363</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>58388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1043,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,7 +1069,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R5" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,27 +1151,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125492610</v>
+        <v>109330664</v>
       </c>
       <c r="B6" t="n">
-        <v>57041</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100091</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R6" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,22 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125491594</v>
+        <v>109330036</v>
       </c>
       <c r="B7" t="n">
-        <v>58080</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,26 +1281,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1313,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R7" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,22 +1347,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,27 +1389,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125491343</v>
+        <v>123596173</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1422,7 +1426,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1432,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R8" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,22 +1466,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125491323</v>
+        <v>109330429</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1545,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1551,13 +1555,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516147</v>
+        <v>515802</v>
       </c>
       <c r="R9" t="n">
-        <v>7058679</v>
+        <v>7058536</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,22 +1585,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,6 +1624,954 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125492212</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125492610</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57340</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125491467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125491333</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125491594</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125491326</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125491343</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125491323</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storbrännbodarna, Öjån, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516147</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7058679</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23313-2025 artfynd.xlsx
+++ b/artfynd/A 23313-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109329758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125492212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109330094</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125492610</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109329712</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491333</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1620,6 +1660,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109330363</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1858,6 +1908,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491326</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1977,6 +2032,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109330664</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2096,6 +2156,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2215,6 +2280,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109330036</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2334,6 +2404,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123596173</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2453,6 +2528,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109330429</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2572,8 +2652,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125491323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>